--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.174" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.174" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.174.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0174.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0174.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.174.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.174" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.174" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 69â€”70</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 167</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L6: isolated marker/symbol line :: /</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]167</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -662,14 +670,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€” 147</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 70â€”71</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • the English Orders</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,13 +685,17 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 0</t>
+          <t>L6: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -717,14 +725,10 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Mode of service of Subpo Ã¦ ena</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ the English Orders</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -736,13 +740,17 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L22: symbol-only separator/garbage line :: , 112</t>
+          <t>L18: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -758,12 +766,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -772,14 +780,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€” 147</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 71 to 74</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -791,13 +795,17 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 115</t>
+          <t>L22: symbol-only separator/garbage line :: , 112</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -830,7 +838,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”147</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 13 to 13</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -842,7 +850,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L26: symbol-only separator/garbage line :: . 116</t>
+          <t>L24: isolated marker/symbol line :: 115</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -881,7 +889,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 71 to 74</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -893,7 +901,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 70</t>
+          <t>L26: symbol-only separator/garbage line :: . 116</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -932,7 +940,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 49â€”50</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -944,7 +952,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 71</t>
+          <t>L30: symbol-only separator/garbage line :: . 69—70</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -983,7 +991,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 13 to 13</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -995,7 +1003,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
+          <t>L32: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1017,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1034,7 +1042,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUBPÅ’NA.â€”WRIT OF</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1046,7 +1054,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: 13</t>
+          <t>L34: symbol-only separator/garbage line :: . 70—71</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1073,7 +1081,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1085,7 +1093,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To appear and answerâ€”form of</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1097,7 +1105,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: e</t>
+          <t>L36: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1119,12 +1127,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1136,7 +1144,7 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1148,7 +1156,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L70: symbol-only separator/garbage line :: .15</t>
+          <t>L52: symbol-only separator/garbage line :: 7. 13</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1187,19 +1195,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 26</t>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L26: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: . 110</t>
+          <t>L54: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1226,7 +1234,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1236,11 +1244,7 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 26â€”27</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L80: symbol-only separator/garbage line :: .73</t>
+          <t>L58: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1287,11 +1291,7 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L82: symbol-only separator/garbage line :: .48</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1338,11 +1338,7 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1352,7 +1348,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 48</t>
+          <t>L70: symbol-only separator/garbage line :: .15</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1389,21 +1385,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L35: symbol-only separator/garbage line :: . 48</t>
+          <t>L31: symbol-only separator/garbage line :: 6 — 147</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L86: symbol-only separator/garbage line :: .49</t>
+          <t>L74: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1428,21 +1420,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢65</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 48</t>
+          <t>L35: symbol-only separator/garbage line :: . 48</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 49</t>
+          <t>L75: symbol-only separator/garbage line :: 6—147</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1467,21 +1455,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L161: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 65â€”66</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 73</t>
+          <t>L38: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 49</t>
+          <t>L80: symbol-only separator/garbage line :: .73</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1506,21 +1490,17 @@
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 49</t>
+          <t>L40: isolated marker/symbol line :: 73</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L94: symbol-only separator/garbage line :: .50</t>
+          <t>L82: symbol-only separator/garbage line :: .48</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1550,12 +1530,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 1</t>
+          <t>L41: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 50</t>
+          <t>L84: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1585,12 +1565,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 49</t>
+          <t>L43: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 3</t>
+          <t>L86: symbol-only separator/garbage line :: .49</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1620,12 +1600,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 3</t>
+          <t>L44: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L136: symbol-only separator/garbage line :: . 109</t>
+          <t>L88: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1655,12 +1635,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L47: symbol-only separator/garbage line :: 49-50</t>
+          <t>L46: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 111</t>
+          <t>L90: symbol-only separator/garbage line :: 49—50</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1690,12 +1670,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 49</t>
+          <t>L47: symbol-only separator/garbage line :: 49-50</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 65</t>
+          <t>L92: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1725,12 +1705,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 50</t>
+          <t>L49: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L94: symbol-only separator/garbage line :: .50</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1760,12 +1740,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L54: symbol-only separator/garbage line :: 50.</t>
+          <t>L53: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L144: symbol-only separator/garbage line :: . 25</t>
+          <t>L96: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1795,12 +1775,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 109</t>
+          <t>L54: symbol-only separator/garbage line :: 50.</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 26</t>
+          <t>L98: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1830,12 +1810,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "111" vs "SUBP NA WRIT OF" :: 111</t>
+          <t>L59: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L136: symbol-only separator/garbage line :: . 109</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1865,12 +1845,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L64: symbol-only separator/garbage line :: . 25</t>
+          <t>L62: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "111" vs "SUBP NA WRIT OF" :: 111</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L137: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1900,12 +1880,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 0</t>
+          <t>L64: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L140: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1935,12 +1915,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 26</t>
+          <t>L67: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 65</t>
+          <t>L142: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1970,12 +1950,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 65</t>
+          <t>L68: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L163: isolated marker/symbol line :: 66</t>
+          <t>L144: symbol-only separator/garbage line :: . 25</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2005,12 +1985,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L71: symbol-only separator/garbage line :: . 26</t>
+          <t>L69: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L165: symbol-only separator/garbage line :: .66</t>
+          <t>L146: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2040,12 +2020,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 0</t>
+          <t>L71: symbol-only separator/garbage line :: . 26</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L167: isolated marker/symbol line :: *</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 26</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2075,12 +2055,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L74: symbol-only separator/garbage line :: 26-27</t>
+          <t>L73: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: 67</t>
+          <t>L149: symbol-only separator/garbage line :: 26—27</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2110,12 +2090,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 27</t>
+          <t>L74: symbol-only separator/garbage line :: 26-27</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L171: symbol-only separator/garbage line :: . 108</t>
+          <t>L151: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2145,12 +2125,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 65</t>
+          <t>L76: isolated marker/symbol line :: 27</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L153: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2180,12 +2160,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 65</t>
+          <t>L77: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: ,</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2215,12 +2195,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: :</t>
+          <t>L78: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: a</t>
+          <t>L157: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: •65</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2250,10 +2230,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 27</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L81: isolated marker/symbol line :: :</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 65</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2281,10 +2265,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L83: symbol-only separator/garbage line :: 65-66</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L82: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L161: symbol-only separator/garbage line :: 65—66</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2312,10 +2300,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 7</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L83: symbol-only separator/garbage line :: 65-66</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L163: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2343,10 +2335,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L84: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L165: symbol-only separator/garbage line :: .66</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2374,10 +2370,14 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 66</t>
-        </is>
-      </c>
-      <c r="O45" s="1" t="inlineStr"/>
+          <t>L86: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr">
+        <is>
+          <t>L167: isolated marker/symbol line :: *</t>
+        </is>
+      </c>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
       <c r="R45" s="1" t="inlineStr"/>
@@ -2405,10 +2405,14 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 28</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="inlineStr"/>
+          <t>L87: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr">
+        <is>
+          <t>L169: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="inlineStr"/>
       <c r="R46" s="1" t="inlineStr"/>
@@ -2436,10 +2440,14 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 66</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L89: isolated marker/symbol line :: 28</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L171: symbol-only separator/garbage line :: . 108</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2467,10 +2475,14 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 29</t>
-        </is>
-      </c>
-      <c r="O48" s="1" t="inlineStr"/>
+          <t>L90: isolated marker/symbol line :: 66</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr">
+        <is>
+          <t>L177: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
       <c r="R48" s="1" t="inlineStr"/>
@@ -2498,10 +2510,14 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 67</t>
-        </is>
-      </c>
-      <c r="O49" s="1" t="inlineStr"/>
+          <t>L92: isolated marker/symbol line :: 29</t>
+        </is>
+      </c>
+      <c r="O49" s="1" t="inlineStr">
+        <is>
+          <t>L179: isolated marker/symbol line :: ,</t>
+        </is>
+      </c>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="inlineStr"/>
       <c r="R49" s="1" t="inlineStr"/>
@@ -2529,10 +2545,14 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 108</t>
-        </is>
-      </c>
-      <c r="O50" s="1" t="inlineStr"/>
+          <t>L94: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
+      <c r="O50" s="1" t="inlineStr">
+        <is>
+          <t>L181: isolated marker/symbol line :: a</t>
+        </is>
+      </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr"/>
       <c r="R50" s="1" t="inlineStr"/>
@@ -2560,7 +2580,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 7.</t>
+          <t>L97: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2591,7 +2611,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: 13</t>
+          <t>L99: isolated marker/symbol line :: 7.</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2622,7 +2642,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 13</t>
+          <t>L100: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2653,7 +2673,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L103: symbol-only separator/garbage line :: . 15</t>
+          <t>L101: isolated marker/symbol line :: 13</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2684,7 +2704,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L105: symbol-only separator/garbage line :: . 110</t>
+          <t>L103: symbol-only separator/garbage line :: . 15</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2715,7 +2735,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L107: symbol-only separator/garbage line :: . 48</t>
+          <t>L105: symbol-only separator/garbage line :: . 110</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2746,7 +2766,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 48</t>
+          <t>L106: symbol-only separator/garbage line :: 6 — 147</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2777,7 +2797,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: 49</t>
+          <t>L107: symbol-only separator/garbage line :: . 48</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -2808,7 +2828,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 49</t>
+          <t>L108: isolated marker/symbol line :: 48</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -2839,7 +2859,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L111: symbol-only separator/garbage line :: 49-50</t>
+          <t>L109: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2870,7 +2890,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 49</t>
+          <t>L110: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2901,7 +2921,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 50</t>
+          <t>L111: symbol-only separator/garbage line :: 49-50</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -2932,7 +2952,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L114: symbol-only separator/garbage line :: 50.</t>
+          <t>L112: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -2963,7 +2983,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 109</t>
+          <t>L113: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -2994,7 +3014,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 111</t>
+          <t>L114: symbol-only separator/garbage line :: 50.</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3025,7 +3045,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 65</t>
+          <t>L115: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3056,7 +3076,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 65</t>
+          <t>L116: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3087,7 +3107,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 65</t>
+          <t>L118: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3118,7 +3138,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L121: symbol-only separator/garbage line :: 65-66</t>
+          <t>L119: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3149,7 +3169,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 66</t>
+          <t>L120: isolated marker/symbol line :: 65</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3180,7 +3200,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L123: isolated marker/symbol line :: 66</t>
+          <t>L121: symbol-only separator/garbage line :: 65-66</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3211,7 +3231,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 67</t>
+          <t>L122: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3242,7 +3262,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 108</t>
+          <t>L123: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3257,6 +3277,68 @@
       <c r="X73" s="1" t="inlineStr"/>
       <c r="Y73" s="1" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr"/>
+      <c r="B74" s="1" t="inlineStr"/>
+      <c r="C74" s="1" t="inlineStr"/>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr"/>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
+      <c r="L74" s="1" t="inlineStr"/>
+      <c r="M74" s="1" t="inlineStr"/>
+      <c r="N74" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
+      <c r="O74" s="1" t="inlineStr"/>
+      <c r="P74" s="1" t="inlineStr"/>
+      <c r="Q74" s="1" t="inlineStr"/>
+      <c r="R74" s="1" t="inlineStr"/>
+      <c r="S74" s="1" t="inlineStr"/>
+      <c r="T74" s="1" t="inlineStr"/>
+      <c r="U74" s="1" t="inlineStr"/>
+      <c r="V74" s="1" t="inlineStr"/>
+      <c r="W74" s="1" t="inlineStr"/>
+      <c r="X74" s="1" t="inlineStr"/>
+      <c r="Y74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr"/>
+      <c r="B75" s="1" t="inlineStr"/>
+      <c r="C75" s="1" t="inlineStr"/>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr"/>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
+      <c r="L75" s="1" t="inlineStr"/>
+      <c r="M75" s="1" t="inlineStr"/>
+      <c r="N75" s="1" t="inlineStr">
+        <is>
+          <t>L125: isolated marker/symbol line :: 108</t>
+        </is>
+      </c>
+      <c r="O75" s="1" t="inlineStr"/>
+      <c r="P75" s="1" t="inlineStr"/>
+      <c r="Q75" s="1" t="inlineStr"/>
+      <c r="R75" s="1" t="inlineStr"/>
+      <c r="S75" s="1" t="inlineStr"/>
+      <c r="T75" s="1" t="inlineStr"/>
+      <c r="U75" s="1" t="inlineStr"/>
+      <c r="V75" s="1" t="inlineStr"/>
+      <c r="W75" s="1" t="inlineStr"/>
+      <c r="X75" s="1" t="inlineStr"/>
+      <c r="Y75" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
